--- a/artfynd/A 42339-2023 artfynd.xlsx
+++ b/artfynd/A 42339-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125535137</v>
       </c>
       <c r="B2" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42339-2023 artfynd.xlsx
+++ b/artfynd/A 42339-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125535137</v>
       </c>
       <c r="B2" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42339-2023 artfynd.xlsx
+++ b/artfynd/A 42339-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125535137</v>
       </c>
       <c r="B2" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
